--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -647,12 +647,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|2</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -693,22 +693,22 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
+        <v>33</v>
+      </c>
+      <c r="L3" t="n">
         <v>42</v>
-      </c>
-      <c r="L3" t="n">
-        <v>45</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -741,16 +741,16 @@
         <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>39.1667</v>
+        <v>38.80955714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|10</t>
+          <t>1|2|24|33|42|49|23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="O4" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -836,19 +836,19 @@
         <v>0.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>38.80955714285714</v>
+        <v>36.1667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1|3|6|38|48|49|15</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
         <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -934,19 +934,19 @@
         <v>0.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>38.6667</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1|9|20|38|42|49|8</t>
+          <t>6|11|20|39|44|49|40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -978,31 +978,31 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L6" t="n">
         <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="O6" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1020,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1032,19 +1032,19 @@
         <v>0.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.33336666666666</v>
+        <v>35.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1|2|24|29|38|49|7</t>
+          <t>3|5|24|37|38|44|19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1076,31 +1076,31 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
+        <v>29</v>
+      </c>
+      <c r="L7" t="n">
         <v>38</v>
-      </c>
-      <c r="L7" t="n">
-        <v>48</v>
       </c>
       <c r="M7" t="n">
         <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O7" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1118,7 +1118,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.0625</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.97439230769231</v>
+        <v>35.5417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|5|24|38|48|49|44</t>
+          <t>8|14|23|29|38|49|36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1174,31 +1174,31 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N8" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0625</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.5417</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|13|24|37|38|49|33</t>
+          <t>3|6|24|31|34|43|10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1272,41 +1272,41 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
+        <v>26</v>
+      </c>
+      <c r="O9" t="n">
+        <v>139</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>42</v>
       </c>
-      <c r="O9" t="n">
-        <v>159</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>47</v>
-      </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.43140588235294</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2|3|24|33|48|49|42</t>
+          <t>3|4|24|29|34|45|26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1376,34 +1376,34 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
+        <v>32</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>46</v>
+      </c>
+      <c r="O10" t="n">
+        <v>133</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>42</v>
-      </c>
-      <c r="M10" t="n">
-        <v>49</v>
-      </c>
-      <c r="N10" t="n">
-        <v>18</v>
-      </c>
-      <c r="O10" t="n">
-        <v>155</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|18</t>
+          <t>3|4|20|29|32|45|46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1471,37 +1471,37 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
+        <v>34</v>
+      </c>
+      <c r="O11" t="n">
+        <v>157</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>47</v>
-      </c>
-      <c r="O11" t="n">
-        <v>155</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>46</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|12|20|33|38|49|47</t>
+          <t>2|13|20|29|44|49|34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1572,10 +1572,10 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>38</v>
@@ -1587,10 +1587,10 @@
         <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O12" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|4|5|38|42|49|6</t>
+          <t>3|8|15|38|42|49|17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|2</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -684,28 +684,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O3" t="n">
         <v>151</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38.80955714285714</v>
+        <v>35.9375</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|2|24|33|42|49|23</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L4" t="n">
         <v>38</v>
       </c>
-      <c r="L4" t="n">
-        <v>44</v>
-      </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N4" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.1667</v>
+        <v>35.74519230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|4|12|25|38|39|15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" t="n">
-        <v>20</v>
-      </c>
       <c r="K5" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
+        <v>38</v>
+      </c>
+      <c r="M5" t="n">
         <v>44</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>49</v>
       </c>
-      <c r="N5" t="n">
-        <v>40</v>
-      </c>
       <c r="O5" t="n">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.97439230769231</v>
+        <v>35.58035714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6|11|20|39|44|49|40</t>
+          <t>3|9|12|25|38|44|49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6667</v>
+        <v>35.4375</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|19</t>
+          <t>3|4|24|29|34|45|27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
         <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="O7" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5417</v>
+        <v>35.3125</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8|14|23|29|38|49|36</t>
+          <t>3|4|20|29|42|45|18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
@@ -1186,19 +1186,19 @@
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.43140588235294</v>
+        <v>35.20220588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|24|31|34|43|10</t>
+          <t>5|6|24|34|39|45|13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.33336666666666</v>
+        <v>35.10416666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|26</t>
+          <t>9|17|20|31|42|46|10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N10" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.24564736842105</v>
+        <v>35.01644736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|4|20|29|32|45|46</t>
+          <t>3|6|24|31|34|43|11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O11" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1667</v>
+        <v>34.9375</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2|13|20|29|44|49|34</t>
+          <t>3|6|15|40|42|49|46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
+        <v>34</v>
+      </c>
+      <c r="L12" t="n">
         <v>38</v>
       </c>
-      <c r="L12" t="n">
-        <v>42</v>
-      </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.09527142857143</v>
+        <v>34.86607142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|17</t>
+          <t>3|5|20|34|38|39|4</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4375</v>
+        <v>74.625</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|5|44|46|49|41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
+        <v>42</v>
+      </c>
+      <c r="M3" t="n">
+        <v>49</v>
+      </c>
+      <c r="N3" t="n">
         <v>38</v>
       </c>
-      <c r="M3" t="n">
-        <v>44</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20</v>
-      </c>
       <c r="O3" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.9375</v>
+        <v>36.125</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>9|11|20|26|42|49|38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.74519230769231</v>
+        <v>35.93269230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|4|12|25|38|39|15</t>
+          <t>3|18|24|34|39|49|2</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
+        <v>34</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39</v>
+      </c>
+      <c r="M5" t="n">
+        <v>45</v>
+      </c>
+      <c r="N5" t="n">
         <v>25</v>
       </c>
-      <c r="L5" t="n">
-        <v>38</v>
-      </c>
-      <c r="M5" t="n">
-        <v>44</v>
-      </c>
-      <c r="N5" t="n">
-        <v>49</v>
-      </c>
       <c r="O5" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.58035714285714</v>
+        <v>35.76785714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|9|12|25|38|44|49</t>
+          <t>3|12|20|34|39|45|25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -984,22 +984,22 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
         <v>139</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.4375</v>
+        <v>35.625</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|27</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
         <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O7" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.3125</v>
+        <v>35.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|4|20|29|42|45|18</t>
+          <t>3|14|21|29|38|46|24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.20220588235294</v>
+        <v>35.38970588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5|6|24|34|39|45|13</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -1275,37 +1275,37 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
         <v>20</v>
       </c>
       <c r="K9" t="n">
+        <v>29</v>
+      </c>
+      <c r="L9" t="n">
+        <v>40</v>
+      </c>
+      <c r="M9" t="n">
+        <v>42</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>161</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>31</v>
-      </c>
-      <c r="L9" t="n">
-        <v>42</v>
-      </c>
-      <c r="M9" t="n">
-        <v>46</v>
-      </c>
-      <c r="N9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" t="n">
-        <v>165</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>37</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.10416666666666</v>
+        <v>35.29166666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9|17|20|31|42|46|10</t>
+          <t>11|19|20|29|40|42|4</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="O10" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.01644736842105</v>
+        <v>35.20394736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|6|24|31|34|43|11</t>
+          <t>3|12|23|34|39|40|48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="N11" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>34.9375</v>
+        <v>35.125</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|6|15|40|42|49|46</t>
+          <t>3|4|24|29|31|34|28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O12" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.86607142857143</v>
+        <v>35.05357142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|5|20|34|38|39|4</t>
+          <t>3|8|15|38|42|49|18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.625</v>
+        <v>74.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|41</t>
+          <t>1|3|5|44|46|49|34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.125</v>
+        <v>38.89285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|11|20|26|42|49|38</t>
+          <t>1|2|20|42|45|49|9</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.93269230769231</v>
+        <v>36.25</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|18|24|34|39|49|2</t>
+          <t>3|8|23|38|44|49|40</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
+        <v>31</v>
+      </c>
+      <c r="L5" t="n">
         <v>34</v>
       </c>
-      <c r="L5" t="n">
-        <v>39</v>
-      </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.76785714285714</v>
+        <v>36.05769230769231</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|25</t>
+          <t>6|15|24|31|34|49|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
         <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="O6" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.625</v>
+        <v>35.75</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|12|20|34|39|45|24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -1082,34 +1082,34 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
         <v>38</v>
       </c>
       <c r="M7" t="n">
+        <v>49</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>139</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>46</v>
-      </c>
-      <c r="N7" t="n">
-        <v>24</v>
-      </c>
-      <c r="O7" t="n">
-        <v>151</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5</v>
+        <v>35.625</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|14|21|29|38|46|24</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
@@ -1192,13 +1192,13 @@
         <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N8" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.38970588235294</v>
+        <v>35.51470588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.29166666666666</v>
+        <v>35.41666666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.20394736842105</v>
+        <v>35.32894736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|12|23|34|39|40|48</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M11" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.125</v>
+        <v>35.25</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|4|24|29|31|34|28</t>
+          <t>10|19|20|28|35|45|5</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.05357142857143</v>
+        <v>35.17857142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|18</t>
+          <t>5|11|20|32|37|44|12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.75</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|34</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38.89285714285714</v>
+        <v>36.3667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|9</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>23</v>
       </c>
       <c r="K4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L4" t="n">
         <v>38</v>
-      </c>
-      <c r="L4" t="n">
-        <v>44</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.25</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|40</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>15</v>
@@ -892,19 +892,19 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
         <v>34</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
         <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.05769230769231</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6|15|24|31|34|49|27</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
         <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.75</v>
+        <v>35.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|24</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1085,22 +1085,22 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.625</v>
+        <v>35.7417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1180,34 +1180,34 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
+        <v>49</v>
+      </c>
+      <c r="N8" t="n">
+        <v>47</v>
+      </c>
+      <c r="O8" t="n">
+        <v>155</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>46</v>
-      </c>
-      <c r="N8" t="n">
-        <v>49</v>
-      </c>
-      <c r="O8" t="n">
-        <v>165</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.51470588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.41666666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>11|19|20|29|40|42|4</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L10" t="n">
         <v>38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>44</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.32894736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="O11" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.25</v>
+        <v>35.3667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>10|19|20|28|35|45|5</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1569,25 +1569,25 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
         <v>11</v>
       </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>149</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.17857142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|11|20|32|37|44|12</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.9333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.3667</v>
+        <v>36.4333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>6|11|20|31|45|46|9</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.17439230769231</v>
+        <v>36.24099230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>6|11|20|38|39|49|8</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.00955714285714</v>
+        <v>36.07615714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
         <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
+        <v>30</v>
+      </c>
+      <c r="M6" t="n">
         <v>38</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>49</v>
       </c>
-      <c r="N6" t="n">
-        <v>9</v>
-      </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.8667</v>
+        <v>35.9333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>3|12|23|25|30|38|49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1079,10 +1079,10 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>20</v>
@@ -1091,13 +1091,13 @@
         <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
         <v>149</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.7417</v>
+        <v>35.8083</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>6|9|20|31|34|49|16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="O8" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.63140588235294</v>
+        <v>35.69800588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|4|24|29|34|45|27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.53336666666667</v>
+        <v>35.59996666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>5|11|20|31|44|46|8</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.44564736842106</v>
+        <v>35.51224736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|20|22|29|38|39|18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
+        <v>32</v>
+      </c>
+      <c r="L11" t="n">
         <v>37</v>
       </c>
-      <c r="L11" t="n">
-        <v>38</v>
-      </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.3667</v>
+        <v>35.4333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|5|20|32|37|44|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="L12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M12" t="n">
         <v>44</v>
       </c>
-      <c r="M12" t="n">
-        <v>49</v>
-      </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O12" t="n">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.29527142857143</v>
+        <v>35.36187142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|11|20|28|31|44|35</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.9333</v>
+        <v>74.6875</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|42</t>
+          <t>1|3|5|44|46|49|17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.4333</v>
+        <v>36.1875</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.24099230769231</v>
+        <v>35.99519230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.07615714285714</v>
+        <v>35.83035714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.9333</v>
+        <v>35.6875</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.8083</v>
+        <v>35.5625</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.69800588235294</v>
+        <v>35.45220588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.59996666666666</v>
+        <v>35.35416666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.51224736842106</v>
+        <v>35.26644736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.4333</v>
+        <v>35.1875</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.36187142857143</v>
+        <v>35.11607142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.6875</v>
+        <v>74.7333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|17</t>
+          <t>1|3|5|44|46|49|30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -687,37 +687,37 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M3" t="n">
+        <v>49</v>
+      </c>
+      <c r="N3" t="n">
+        <v>43</v>
+      </c>
+      <c r="O3" t="n">
+        <v>165</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>46</v>
-      </c>
-      <c r="N3" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>159</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>40</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1875</v>
+        <v>36.2333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6|11|20|31|45|46|9</t>
+          <t>3|5|24|38|46|49|43</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.99519230769231</v>
+        <v>36.04099230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6|11|20|38|39|49|8</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O5" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.83035714285714</v>
+        <v>35.87615714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|10|24|33|38|49|35</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
         <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6875</v>
+        <v>35.7333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|23|25|30|38|49</t>
+          <t>9|11|20|32|38|45|49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
         <v>34</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5625</v>
+        <v>35.6083</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|9|20|31|34|49|16</t>
+          <t>3|4|24|29|34|45|27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N8" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="O8" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.45220588235294</v>
+        <v>35.49800588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|27</t>
+          <t>5|6|24|31|32|37|40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1275,37 +1275,37 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M9" t="n">
+        <v>49</v>
+      </c>
+      <c r="N9" t="n">
+        <v>38</v>
+      </c>
+      <c r="O9" t="n">
+        <v>153</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>46</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>157</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>41</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.35416666666666</v>
+        <v>35.39996666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|11|20|31|44|46|8</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J10" t="n">
         <v>20</v>
       </c>
-      <c r="J10" t="n">
-        <v>22</v>
-      </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.26644736842105</v>
+        <v>35.31224736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|22|29|38|39|18</t>
+          <t>2|11|20|32|35|45|30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O11" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1875</v>
+        <v>35.2333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|5|20|32|37|44|12</t>
+          <t>2|13|24|37|38|49|28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
         <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.11607142857143</v>
+        <v>35.16187142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|11|20|28|31|44|35</t>
+          <t>3|5|20|32|37|44|12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.7333</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|30</t>
+          <t>1|3|5|44|46|49|46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -687,10 +687,10 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -699,16 +699,16 @@
         <v>38</v>
       </c>
       <c r="L3" t="n">
+        <v>45</v>
+      </c>
+      <c r="M3" t="n">
         <v>46</v>
       </c>
-      <c r="M3" t="n">
-        <v>49</v>
-      </c>
       <c r="N3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.2333</v>
+        <v>36.1</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|5|24|38|46|49|43</t>
+          <t>1|3|24|38|45|46|44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -791,22 +791,22 @@
         <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="O4" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.04099230769231</v>
+        <v>35.90769230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
         <v>38</v>
       </c>
       <c r="M5" t="n">
+        <v>45</v>
+      </c>
+      <c r="N5" t="n">
         <v>49</v>
       </c>
-      <c r="N5" t="n">
-        <v>35</v>
-      </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.87615714285714</v>
+        <v>35.74285714285715</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|10|24|33|38|49|35</t>
+          <t>3|12|13|34|38|45|49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.7333</v>
+        <v>35.6</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|11|20|32|38|45|49</t>
+          <t>3|6|21|34|40|49|41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O7" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.6083</v>
+        <v>35.475</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|27</t>
+          <t>3|6|24|25|31|44|15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
@@ -1186,28 +1186,28 @@
         <v>24</v>
       </c>
       <c r="K8" t="n">
+        <v>25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>34</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" t="n">
+        <v>125</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>31</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32</v>
-      </c>
-      <c r="M8" t="n">
-        <v>37</v>
-      </c>
-      <c r="N8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O8" t="n">
-        <v>135</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>32</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.49800588235294</v>
+        <v>35.36470588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5|6|24|31|32|37|40</t>
+          <t>3|6|24|25|33|34|30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.39996666666666</v>
+        <v>35.26666666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>6|9|18|33|40|49|17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
         <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>11</v>
@@ -1382,19 +1382,19 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O10" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.31224736842105</v>
+        <v>35.17894736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2|11|20|32|35|45|30</t>
+          <t>6|11|20|38|43|49|41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M11" t="n">
+        <v>42</v>
+      </c>
+      <c r="N11" t="n">
         <v>49</v>
       </c>
-      <c r="N11" t="n">
-        <v>28</v>
-      </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.2333</v>
+        <v>35.1</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2|13|24|37|38|49|28</t>
+          <t>9|18|24|25|33|42|49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1569,25 +1569,25 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
+        <v>34</v>
+      </c>
+      <c r="M12" t="n">
         <v>37</v>
       </c>
-      <c r="M12" t="n">
-        <v>44</v>
-      </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="O12" t="n">
         <v>141</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.16187142857143</v>
+        <v>35.02857142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|5|20|32|37|44|12</t>
+          <t>6|9|24|31|34|37|48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.59999999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|46</t>
+          <t>1|3|5|44|46|49|37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
         <v>45</v>
@@ -705,10 +705,10 @@
         <v>46</v>
       </c>
       <c r="N3" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1</v>
+        <v>36.1667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|3|24|38|45|46|44</t>
+          <t>11|18|20|29|45|46|27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N4" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.90769230769231</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>3|12|14|37|38|39|13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
+        <v>31</v>
+      </c>
+      <c r="L5" t="n">
         <v>34</v>
-      </c>
-      <c r="L5" t="n">
-        <v>38</v>
       </c>
       <c r="M5" t="n">
         <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.74285714285715</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|12|13|34|38|45|49</t>
+          <t>15|20|24|31|34|45|9</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
+        <v>46</v>
+      </c>
+      <c r="N6" t="n">
         <v>49</v>
       </c>
-      <c r="N6" t="n">
-        <v>41</v>
-      </c>
       <c r="O6" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6</v>
+        <v>35.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|6|21|34|40|49|41</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1085,22 +1085,22 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.475</v>
+        <v>35.5417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|24|25|31|44|15</t>
+          <t>3|6|18|38|43|49|2</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O8" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.36470588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|24|25|33|34|30</t>
+          <t>2|3|24|29|36|49|15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1278,22 +1278,22 @@
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
         <v>155</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.26666666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6|9|18|33|40|49|17</t>
+          <t>6|19|20|31|35|44|15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>18</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>6</v>
       </c>
-      <c r="I10" t="n">
-        <v>11</v>
-      </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L10" t="n">
         <v>38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>43</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="O10" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.17894736842106</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6|11|20|38|43|49|41</t>
+          <t>3|6|19|32|38|49|24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
         <v>9</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>18</v>
       </c>
-      <c r="J11" t="n">
-        <v>24</v>
-      </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="O11" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1</v>
+        <v>35.1667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9|18|24|25|33|42|49</t>
+          <t>3|9|18|38|40|49|36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
         <v>6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>24</v>
       </c>
       <c r="K12" t="n">
         <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.02857142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6|9|24|31|34|37|48</t>
+          <t>1|3|6|31|38|46|15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|37</t>
+          <t>1|3|5|44|46|49|47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -687,37 +687,37 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M3" t="n">
+        <v>49</v>
+      </c>
+      <c r="N3" t="n">
+        <v>44</v>
+      </c>
+      <c r="O3" t="n">
+        <v>165</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>46</v>
-      </c>
-      <c r="N3" t="n">
-        <v>27</v>
-      </c>
-      <c r="O3" t="n">
-        <v>169</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>35</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1667</v>
+        <v>36.3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>11|18|20|29|45|46|27</t>
+          <t>3|5|24|38|46|49|44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M4" t="n">
         <v>39</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O4" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.97439230769231</v>
+        <v>36.1076923076923</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|12|14|37|38|39|13</t>
+          <t>3|18|24|29|34|39|27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.80955714285714</v>
+        <v>35.94285714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>15|20|24|31|34|45|9</t>
+          <t>3|5|24|36|37|40|49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6667</v>
+        <v>35.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|6|20|29|44|45|23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5417</v>
+        <v>35.675</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|18|38|43|49|2</t>
+          <t>1|11|20|40|44|45|3</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O8" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.43140588235294</v>
+        <v>35.56470588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|3|24|29|36|49|15</t>
+          <t>6|9|24|31|44|49|20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
         <v>6</v>
       </c>
-      <c r="I9" t="n">
-        <v>19</v>
-      </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="O9" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.33336666666666</v>
+        <v>35.46666666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6|19|20|31|35|44|15</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
         <v>24</v>
       </c>
       <c r="O10" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.24564736842105</v>
+        <v>35.37894736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|6|19|32|38|49|24</t>
+          <t>3|11|20|28|38|45|24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
+        <v>31</v>
+      </c>
+      <c r="L11" t="n">
+        <v>44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>46</v>
+      </c>
+      <c r="N11" t="n">
         <v>38</v>
       </c>
-      <c r="L11" t="n">
-        <v>40</v>
-      </c>
-      <c r="M11" t="n">
-        <v>49</v>
-      </c>
-      <c r="N11" t="n">
-        <v>36</v>
-      </c>
       <c r="O11" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1667</v>
+        <v>35.3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|9|18|38|40|49|36</t>
+          <t>1|11|20|31|44|46|38</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1569,37 +1569,37 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
         <v>38</v>
       </c>
       <c r="M12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>147</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>46</v>
-      </c>
-      <c r="N12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O12" t="n">
-        <v>125</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.09527142857143</v>
+        <v>35.22857142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1|3|6|31|38|46|15</t>
+          <t>3|6|19|32|38|49|24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.8</v>
+        <v>74.5333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|47</t>
+          <t>1|3|5|44|46|49|45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -690,25 +690,25 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.3</v>
+        <v>36.0333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|5|24|38|46|49|44</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N4" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.1076923076923</v>
+        <v>35.8409923076923</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|18|24|29|34|39|27</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.94285714285714</v>
+        <v>35.67615714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|5|24|36|37|40|49</t>
+          <t>1|11|20|40|44|45|3</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
         <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.8</v>
+        <v>35.5333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|6|20|29|44|45|23</t>
+          <t>3|20|22|29|38|39|18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="O7" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.675</v>
+        <v>35.4083</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1|11|20|40|44|45|3</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" t="n">
         <v>49</v>
       </c>
-      <c r="N8" t="n">
-        <v>20</v>
-      </c>
       <c r="O8" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.56470588235294</v>
+        <v>35.29800588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|9|24|31|44|49|20</t>
+          <t>3|12|13|34|38|45|49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.46666666666667</v>
+        <v>35.19996666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>5|6|20|31|44|45|11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.37894736842105</v>
+        <v>35.11224736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|11|20|28|38|45|24</t>
+          <t>3|20|24|29|34|49|8</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="O11" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.3</v>
+        <v>35.0333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|11|20|31|44|46|38</t>
+          <t>3|4|20|29|42|45|19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.22857142857143</v>
+        <v>34.96187142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|6|19|32|38|49|24</t>
+          <t>3|15|24|25|36|42|10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5333</v>
+        <v>74.6875</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|45</t>
+          <t>1|3|5|44|46|49|39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.0333</v>
+        <v>36.1875</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.8409923076923</v>
+        <v>35.99519230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.67615714285714</v>
+        <v>35.83035714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.5333</v>
+        <v>35.6875</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.4083</v>
+        <v>35.5625</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.29800588235294</v>
+        <v>35.45220588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.19996666666667</v>
+        <v>35.35416666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.11224736842105</v>
+        <v>35.26644736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.0333</v>
+        <v>35.1875</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.96187142857143</v>
+        <v>35.11607142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.6875</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|39</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -690,25 +690,25 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1875</v>
+        <v>36.3667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -788,34 +788,34 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
         <v>38</v>
       </c>
       <c r="M4" t="n">
+        <v>49</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O4" t="n">
+        <v>151</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>46</v>
-      </c>
-      <c r="N4" t="n">
-        <v>49</v>
-      </c>
-      <c r="O4" t="n">
-        <v>165</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.99519230769231</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.83035714285714</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1|11|20|40|44|45|3</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
         <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6875</v>
+        <v>35.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|20|22|29|38|39|18</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1085,22 +1085,22 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5625</v>
+        <v>35.7417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.45220588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|12|13|34|38|45|49</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.35416666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|6|20|31|44|45|11</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.26644736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|24|29|34|49|8</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="O11" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1875</v>
+        <v>35.3667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|4|20|29|42|45|19</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.11607142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|15|24|25|36|42|10</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O3" t="n">
         <v>165</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.3667</v>
+        <v>36.1667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|8|23|38|44|49|36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M4" t="n">
+        <v>40</v>
+      </c>
+      <c r="N4" t="n">
         <v>49</v>
       </c>
-      <c r="N4" t="n">
-        <v>17</v>
-      </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.17439230769231</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>3|5|24|36|37|40|49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -892,19 +892,19 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
         <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.00955714285714</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>3|15|24|30|38|49|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
         <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.8667</v>
+        <v>35.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>3|12|20|29|31|44|35</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="n">
+        <v>37</v>
+      </c>
+      <c r="L7" t="n">
+        <v>38</v>
+      </c>
+      <c r="M7" t="n">
+        <v>44</v>
+      </c>
+      <c r="N7" t="n">
         <v>20</v>
       </c>
-      <c r="K7" t="n">
-        <v>31</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>45</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.7417</v>
+        <v>35.5417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="O8" t="n">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.63140588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|4|5|31|44|46|15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.53336666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|15|18|34|45|46|5</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.44564736842106</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|20|22|29|38|39|18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1474,34 +1474,34 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
+        <v>49</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>149</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>46</v>
-      </c>
-      <c r="N11" t="n">
-        <v>49</v>
-      </c>
-      <c r="O11" t="n">
-        <v>165</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.3667</v>
+        <v>35.1667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
         <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="O12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.29527142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|47</t>
+          <t>1|3|5|44|46|49|15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1667</v>
+        <v>38.94285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|36</t>
+          <t>1|2|20|42|45|49|9</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="O4" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.97439230769231</v>
+        <v>36.3</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|5|24|36|37|40|49</t>
+          <t>6|15|24|31|34|49|29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
         <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.80955714285714</v>
+        <v>36.1076923076923</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|15|24|30|38|49|27</t>
+          <t>6|11|20|39|44|49|38</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -990,19 +990,19 @@
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6667</v>
+        <v>35.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|20|29|31|44|35</t>
+          <t>3|12|20|34|39|45|27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5417</v>
+        <v>35.675</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|18|24|29|44|49|35</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
+        <v>39</v>
+      </c>
+      <c r="M8" t="n">
         <v>44</v>
       </c>
-      <c r="M8" t="n">
-        <v>46</v>
-      </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="O8" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.43140588235294</v>
+        <v>35.56470588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|4|5|31|44|46|15</t>
+          <t>11|18|20|29|39|44|49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1278,34 +1278,34 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
         <v>15</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
+        <v>46</v>
+      </c>
+      <c r="M9" t="n">
+        <v>49</v>
+      </c>
+      <c r="N9" t="n">
         <v>45</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
+        <v>153</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>46</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>161</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.33336666666666</v>
+        <v>35.46666666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|15|18|34|45|46|5</t>
+          <t>3|6|15|34|46|49|45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1376,22 +1376,22 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O10" t="n">
         <v>151</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.24564736842105</v>
+        <v>35.37894736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|22|29|38|39|18</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
+        <v>25</v>
+      </c>
+      <c r="L11" t="n">
         <v>38</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>44</v>
       </c>
-      <c r="M11" t="n">
-        <v>49</v>
-      </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O11" t="n">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1667</v>
+        <v>35.3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|12|15|25|38|44|13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M12" t="n">
         <v>46</v>
       </c>
-      <c r="M12" t="n">
-        <v>49</v>
-      </c>
       <c r="N12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.09527142857143</v>
+        <v>35.22857142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>3|12|17|38|39|46|35</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.8</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|15</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="O3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38.94285714285714</v>
+        <v>36.1667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|9</t>
+          <t>3|18|24|33|35|38|27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>11</v>
       </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>15</v>
-      </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.3</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6|15|24|31|34|49|29</t>
+          <t>2|11|18|38|45|49|41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N5" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.1076923076923</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6|11|20|39|44|49|38</t>
+          <t>1|3|18|38|45|46|8</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="O6" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.8</v>
+        <v>35.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|27</t>
+          <t>3|15|20|29|38|46|17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
         <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O7" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.675</v>
+        <v>35.5417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|18|24|29|44|49|35</t>
+          <t>3|12|20|31|44|45|32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
         <v>18</v>
       </c>
-      <c r="J8" t="n">
-        <v>20</v>
-      </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O8" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.56470588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>11|18|20|29|39|44|49</t>
+          <t>3|5|18|38|44|49|33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.46666666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|15|34|46|49|45</t>
+          <t>9|11|18|33|42|44|17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.37894736842105</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1477,22 +1477,22 @@
         <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
         <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.3</v>
+        <v>35.1667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|12|15|25|38|44|13</t>
+          <t>3|12|24|37|38|45|32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L12" t="n">
         <v>38</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>39</v>
       </c>
-      <c r="M12" t="n">
-        <v>46</v>
-      </c>
       <c r="N12" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.22857142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|12|17|38|39|46|35</t>
+          <t>3|15|18|36|38|39|10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1667</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.97439230769231</v>
+        <v>35.80769230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.80955714285714</v>
+        <v>35.64285714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6667</v>
+        <v>35.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5417</v>
+        <v>35.375</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.43140588235294</v>
+        <v>35.26470588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.33336666666666</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.24564736842105</v>
+        <v>35.07894736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1667</v>
+        <v>35</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.09527142857143</v>
+        <v>34.92857142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5</v>
+        <v>74.4375</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.0625</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>38.3125</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|18|24|33|35|38|27</t>
+          <t>1|3|6|38|42|49|9</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.80769230769231</v>
+        <v>35.9375</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2|11|18|38|45|49|41</t>
+          <t>6|11|20|39|40|49|8</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -880,28 +880,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
+        <v>33</v>
+      </c>
+      <c r="L5" t="n">
+        <v>35</v>
+      </c>
+      <c r="M5" t="n">
         <v>38</v>
       </c>
-      <c r="L5" t="n">
-        <v>45</v>
-      </c>
-      <c r="M5" t="n">
-        <v>46</v>
-      </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="O5" t="n">
         <v>151</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.64285714285714</v>
+        <v>35.74519230769231</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1|3|18|38|45|46|8</t>
+          <t>3|18|24|33|35|38|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -978,31 +978,31 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1020,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.5</v>
+        <v>35.58035714285714</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|15|20|29|38|46|17</t>
+          <t>2|11|20|33|34|45|49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1076,31 +1076,31 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1118,7 +1118,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0625</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.375</v>
+        <v>35.4375</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|12|20|31|44|45|32</t>
+          <t>2|3|24|33|42|49|27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.26470588235294</v>
+        <v>35.20220588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|5|18|38|44|49|33</t>
+          <t>3|12|20|31|44|45|32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
+        <v>37</v>
+      </c>
+      <c r="L9" t="n">
+        <v>38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>49</v>
+      </c>
+      <c r="N9" t="n">
         <v>33</v>
       </c>
-      <c r="L9" t="n">
-        <v>42</v>
-      </c>
-      <c r="M9" t="n">
-        <v>44</v>
-      </c>
-      <c r="N9" t="n">
-        <v>17</v>
-      </c>
       <c r="O9" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.16666666666666</v>
+        <v>35.10416666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9|11|18|33|42|44|17</t>
+          <t>2|13|24|37|38|49|33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.07894736842105</v>
+        <v>35.01644736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>2|11|18|42|45|49|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35</v>
+        <v>34.9375</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|12|24|37|38|45|32</t>
+          <t>6|11|18|29|40|49|46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
         <v>38</v>
       </c>
       <c r="M12" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="O12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.92857142857143</v>
+        <v>34.86607142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|15|18|36|38|39|10</t>
+          <t>3|12|13|32|38|49|41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4375</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0625</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38.3125</v>
+        <v>36.3667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|3|6|38|42|49|9</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.9375</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6|11|20|39|40|49|8</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
         <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.74519230769231</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|18|24|33|35|38|27</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -978,31 +978,31 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1020,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.58035714285714</v>
+        <v>35.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|11|20|33|34|45|49</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1076,41 +1076,41 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>149</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>42</v>
       </c>
-      <c r="M7" t="n">
-        <v>49</v>
-      </c>
-      <c r="N7" t="n">
-        <v>27</v>
-      </c>
-      <c r="O7" t="n">
-        <v>153</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>47</v>
-      </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.4375</v>
+        <v>35.7417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2|3|24|33|42|49|27</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O8" t="n">
         <v>155</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.20220588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|12|20|31|44|45|32</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1275,16 +1275,16 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
         <v>38</v>
@@ -1293,10 +1293,10 @@
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.10416666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2|13|24|37|38|49|33</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.01644736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2|11|18|42|45|49|4</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
+        <v>46</v>
+      </c>
+      <c r="N11" t="n">
         <v>49</v>
       </c>
-      <c r="N11" t="n">
-        <v>46</v>
-      </c>
       <c r="O11" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>34.9375</v>
+        <v>35.3667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|11|18|29|40|49|46</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
         <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.86607142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|12|13|32|38|49|41</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|42|44|46|49|34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
+        <v>34</v>
+      </c>
+      <c r="L3" t="n">
         <v>38</v>
-      </c>
-      <c r="L3" t="n">
-        <v>44</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.3667</v>
+        <v>38.5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>1|3|12|34|38|49|15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.17439230769231</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>3|8|24|38|39|49|16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.00955714285714</v>
+        <v>35.80769230769231</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>3|18|24|38|39|45|47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -978,31 +978,31 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
         <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1020,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.8667</v>
+        <v>35.64285714285714</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>3|6|23|38|40|49|45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.7417</v>
+        <v>35.375</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>11|18|20|29|45|46|15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1177,16 +1177,16 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8" t="n">
         <v>40</v>
@@ -1195,10 +1195,10 @@
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.63140588235294</v>
+        <v>35.26470588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>6|11|20|39|40|49|8</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="O9" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.53336666666667</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|12|20|34|39|45|27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.44564736842106</v>
+        <v>35.07894736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|12|24|34|45|49|48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
+        <v>32</v>
+      </c>
+      <c r="L11" t="n">
         <v>37</v>
       </c>
-      <c r="L11" t="n">
-        <v>38</v>
-      </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N11" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="O11" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.3667</v>
+        <v>35</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|18|24|32|37|39|41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N12" t="n">
         <v>49</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
       <c r="O12" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.29527142857143</v>
+        <v>34.92857142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>2|11|20|33|34|45|49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5</v>
+        <v>74.4667</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|34</t>
+          <t>1|3|42|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38.5</v>
+        <v>35.9667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|3|12|34|38|49|15</t>
+          <t>3|18|24|38|39|45|47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>35.77439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|8|24|38|39|49|16</t>
+          <t>3|18|24|35|40|49|2</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -892,19 +892,19 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
+        <v>37</v>
+      </c>
+      <c r="M5" t="n">
         <v>39</v>
       </c>
-      <c r="M5" t="n">
-        <v>45</v>
-      </c>
       <c r="N5" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.80769230769231</v>
+        <v>35.60955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|18|24|38|39|45|47</t>
+          <t>3|18|24|32|37|39|41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -978,31 +978,31 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L6" t="n">
         <v>38</v>
       </c>
-      <c r="L6" t="n">
-        <v>40</v>
-      </c>
       <c r="M6" t="n">
+        <v>45</v>
+      </c>
+      <c r="N6" t="n">
         <v>49</v>
       </c>
-      <c r="N6" t="n">
-        <v>45</v>
-      </c>
       <c r="O6" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1020,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.64285714285714</v>
+        <v>35.4667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|6|23|38|40|49|45</t>
+          <t>3|12|14|37|38|45|49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
         <v>18</v>
       </c>
-      <c r="J7" t="n">
-        <v>20</v>
-      </c>
       <c r="K7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L7" t="n">
         <v>29</v>
       </c>
-      <c r="L7" t="n">
-        <v>45</v>
-      </c>
       <c r="M7" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.375</v>
+        <v>35.3417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>11|18|20|29|45|46|15</t>
+          <t>3|12|18|25|29|38|24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="n">
-        <v>11</v>
-      </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="O8" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.26470588235294</v>
+        <v>35.23140588235295</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|11|20|39|40|49|8</t>
+          <t>3|6|24|33|44|49|34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
         <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.16666666666666</v>
+        <v>35.13336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|27</t>
+          <t>6|20|21|33|42|45|13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
+        <v>42</v>
+      </c>
+      <c r="M10" t="n">
         <v>45</v>
       </c>
-      <c r="M10" t="n">
-        <v>49</v>
-      </c>
       <c r="N10" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O10" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.07894736842105</v>
+        <v>35.04564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|12|24|34|45|49|48</t>
+          <t>4|19|20|31|42|45|33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="O11" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35</v>
+        <v>34.9667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|18|24|32|37|39|41</t>
+          <t>11|16|20|29|38|45|35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.92857142857143</v>
+        <v>34.89527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|11|20|33|34|45|49</t>
+          <t>3|6|21|32|40|49|9</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O2" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4667</v>
+        <v>74.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|32</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="O3" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.9667</v>
+        <v>36.3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|18|24|38|39|45|47</t>
+          <t>6|11|20|39|44|49|40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.77439230769231</v>
+        <v>36.1076923076923</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|18|24|35|40|49|2</t>
+          <t>3|18|24|25|34|37|9</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.60955714285714</v>
+        <v>35.94285714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|18|24|32|37|39|41</t>
+          <t>3|6|20|34|43|45|16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -984,10 +984,10 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
         <v>37</v>
@@ -999,10 +999,10 @@
         <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.4667</v>
+        <v>35.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|14|37|38|45|49</t>
+          <t>3|4|20|37|38|45|27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L7" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.3417</v>
+        <v>35.675</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|12|18|25|29|38|24</t>
+          <t>3|20|21|37|38|42|35</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.23140588235295</v>
+        <v>35.56470588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|24|33|44|49|34</t>
+          <t>2|3|15|38|46|49|29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" t="n">
         <v>20</v>
       </c>
-      <c r="J9" t="n">
-        <v>21</v>
-      </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.13336666666666</v>
+        <v>35.46666666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6|20|21|33|42|45|13</t>
+          <t>3|18|20|29|37|38|7</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.04564736842106</v>
+        <v>35.37894736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4|19|20|31|42|45|33</t>
+          <t>3|6|20|33|38|49|26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1471,10 +1471,10 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
@@ -1483,16 +1483,16 @@
         <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
         <v>35</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>34.9667</v>
+        <v>35.3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>11|16|20|29|38|45|35</t>
+          <t>3|18|20|29|42|49|35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.89527142857143</v>
+        <v>35.22857142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|6|21|32|40|49|9</t>
+          <t>3|19|24|28|35|38|20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.8</v>
+        <v>74.7333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|42|44|46|49|17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
         <v>44</v>
@@ -705,10 +705,10 @@
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.3</v>
+        <v>36.2333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6|11|20|39|44|49|40</t>
+          <t>3|8|23|38|44|49|37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L4" t="n">
+        <v>45</v>
+      </c>
+      <c r="M4" t="n">
+        <v>49</v>
+      </c>
+      <c r="N4" t="n">
         <v>34</v>
       </c>
-      <c r="M4" t="n">
-        <v>37</v>
-      </c>
-      <c r="N4" t="n">
-        <v>9</v>
-      </c>
       <c r="O4" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.1076923076923</v>
+        <v>36.04099230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|18|24|25|34|37|9</t>
+          <t>3|6|20|32|45|49|34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
         <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O5" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.94285714285714</v>
+        <v>35.87615714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|6|20|34|43|45|16</t>
+          <t>3|12|24|38|39|45|32</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -984,10 +984,10 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
         <v>37</v>
@@ -996,13 +996,13 @@
         <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="O6" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.8</v>
+        <v>35.7333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|4|20|37|38|45|27</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J7" t="n">
         <v>20</v>
       </c>
-      <c r="J7" t="n">
-        <v>21</v>
-      </c>
       <c r="K7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.675</v>
+        <v>35.6083</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|20|21|37|38|42|35</t>
+          <t>3|11|20|40|42|49|9</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.56470588235294</v>
+        <v>35.49800588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|3|15|38|46|49|29</t>
+          <t>3|6|20|31|40|45|13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="O9" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.46666666666667</v>
+        <v>35.39996666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|18|20|29|37|38|7</t>
+          <t>6|20|21|31|45|46|32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J10" t="n">
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="O10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.37894736842105</v>
+        <v>35.31224736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|6|20|33|38|49|26</t>
+          <t>3|15|20|29|38|46|17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1474,19 +1474,19 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
+        <v>38</v>
+      </c>
+      <c r="M11" t="n">
         <v>42</v>
-      </c>
-      <c r="M11" t="n">
-        <v>49</v>
       </c>
       <c r="N11" t="n">
         <v>35</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.3</v>
+        <v>35.2333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|18|20|29|42|49|35</t>
+          <t>3|20|21|37|38|42|35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="O12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.22857142857143</v>
+        <v>35.16187142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|19|24|28|35|38|20</t>
+          <t>3|15|24|32|38|45|44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.7333</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|17</t>
+          <t>1|3|5|44|46|49|4</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
+        <v>42</v>
+      </c>
+      <c r="M3" t="n">
         <v>44</v>
       </c>
-      <c r="M3" t="n">
-        <v>49</v>
-      </c>
       <c r="N3" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.2333</v>
+        <v>36.1</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|37</t>
+          <t>11|20|21|29|42|44|48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>45</v>
-      </c>
-      <c r="M4" t="n">
-        <v>49</v>
       </c>
       <c r="N4" t="n">
         <v>34</v>
       </c>
       <c r="O4" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.04099230769231</v>
+        <v>35.90769230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|6|20|32|45|49|34</t>
+          <t>3|18|24|31|38|45|34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.87615714285714</v>
+        <v>35.74285714285715</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|12|24|38|39|45|32</t>
+          <t>3|8|20|29|44|49|30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
         <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.7333</v>
+        <v>35.6</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|15|18|36|38|39|10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
@@ -1088,7 +1088,7 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L7" t="n">
         <v>42</v>
@@ -1097,10 +1097,10 @@
         <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="O7" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.6083</v>
+        <v>35.475</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|11|20|40|42|49|9</t>
+          <t>9|11|20|28|42|49|37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.49800588235294</v>
+        <v>35.36470588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|20|31|40|45|13</t>
+          <t>3|12|20|33|38|49|46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O9" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.39996666666666</v>
+        <v>35.26666666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6|20|21|31|45|46|32</t>
+          <t>2|3|15|38|46|49|28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
+        <v>18</v>
+      </c>
+      <c r="K10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L10" t="n">
+        <v>44</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
         <v>20</v>
       </c>
-      <c r="K10" t="n">
-        <v>29</v>
-      </c>
-      <c r="L10" t="n">
-        <v>38</v>
-      </c>
-      <c r="M10" t="n">
-        <v>46</v>
-      </c>
-      <c r="N10" t="n">
-        <v>17</v>
-      </c>
       <c r="O10" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.31224736842105</v>
+        <v>35.17894736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|15|20|29|38|46|17</t>
+          <t>3|7|18|38|44|45|20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
+        <v>26</v>
+      </c>
+      <c r="L11" t="n">
         <v>37</v>
       </c>
-      <c r="L11" t="n">
-        <v>38</v>
-      </c>
       <c r="M11" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="O11" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.2333</v>
+        <v>35.1</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|20|21|37|38|42|35</t>
+          <t>3|8|18|26|37|49|24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L12" t="n">
         <v>32</v>
       </c>
-      <c r="L12" t="n">
-        <v>38</v>
-      </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.16187142857143</v>
+        <v>35.02857142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|15|24|32|38|45|44</t>
+          <t>1|2|21|25|32|44|9</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.59999999999999</v>
+        <v>74.4375</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|4</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1</v>
+        <v>35.9375</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.90769230769231</v>
+        <v>35.74519230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.74285714285715</v>
+        <v>35.58035714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6</v>
+        <v>35.4375</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.475</v>
+        <v>35.3125</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.36470588235294</v>
+        <v>35.20220588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.26666666666667</v>
+        <v>35.10416666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.17894736842106</v>
+        <v>35.01644736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1</v>
+        <v>34.9375</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.02857142857143</v>
+        <v>34.86607142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4375</v>
+        <v>74.5625</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -684,41 +684,41 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
         <v>20</v>
       </c>
-      <c r="J3" t="n">
-        <v>21</v>
-      </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>161</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>48</v>
       </c>
-      <c r="O3" t="n">
-        <v>167</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>33</v>
-      </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.9375</v>
+        <v>38.70535714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>11|20|21|29|42|44|48</t>
+          <t>1|8|20|38|45|49|3</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -794,19 +794,19 @@
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" t="n">
         <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.74519230769231</v>
+        <v>36.0625</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|18|24|31|38|45|34</t>
+          <t>3|18|24|38|39|45|47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
+        <v>45</v>
+      </c>
+      <c r="N5" t="n">
         <v>49</v>
       </c>
-      <c r="N5" t="n">
-        <v>30</v>
-      </c>
       <c r="O5" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.58035714285714</v>
+        <v>35.87019230769231</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|8|20|29|44|49|30</t>
+          <t>3|12|14|37|38|45|49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="O6" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.4375</v>
+        <v>35.5625</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|15|18|36|38|39|10</t>
+          <t>3|12|20|31|45|46|34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
         <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="O7" t="n">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.3125</v>
+        <v>35.4375</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9|11|20|28|42|49|37</t>
+          <t>3|6|15|26|38|49|13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
         <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O8" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.20220588235294</v>
+        <v>35.32720588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|12|20|33|38|49|46</t>
+          <t>11|16|20|29|38|45|36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.10416666666666</v>
+        <v>35.22916666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2|3|15|38|46|49|28</t>
+          <t>3|18|20|26|45|49|17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
+        <v>32</v>
+      </c>
+      <c r="M10" t="n">
+        <v>37</v>
+      </c>
+      <c r="N10" t="n">
         <v>44</v>
       </c>
-      <c r="M10" t="n">
-        <v>45</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20</v>
-      </c>
       <c r="O10" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.01644736842105</v>
+        <v>35.14144736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|7|18|38|44|45|20</t>
+          <t>3|12|20|31|32|37|44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="O11" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>34.9375</v>
+        <v>35.0625</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|8|18|26|37|49|24</t>
+          <t>3|18|24|27|40|49|38</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.86607142857143</v>
+        <v>34.99107142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1|2|21|25|32|44|9</t>
+          <t>3|5|22|34|37|40|11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5625</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|17</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38.70535714285714</v>
+        <v>36.3667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|8|20|38|45|49|3</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L4" t="n">
         <v>38</v>
       </c>
-      <c r="L4" t="n">
-        <v>39</v>
-      </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.0625</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|18|24|38|39|45|47</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.87019230769231</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|12|14|37|38|45|49</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -987,31 +987,31 @@
         <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
+        <v>49</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>155</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>46</v>
-      </c>
-      <c r="N6" t="n">
-        <v>34</v>
-      </c>
-      <c r="O6" t="n">
-        <v>157</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>43</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.5625</v>
+        <v>35.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|20|31|45|46|34</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1085,22 +1085,22 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.4375</v>
+        <v>35.7417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|15|26|38|49|13</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="O8" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.32720588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>11|16|20|29|38|45|36</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.22916666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|18|20|26|45|49|17</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23</v>
+      </c>
+      <c r="K10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L10" t="n">
+        <v>38</v>
+      </c>
+      <c r="M10" t="n">
+        <v>49</v>
+      </c>
+      <c r="N10" t="n">
         <v>12</v>
       </c>
-      <c r="J10" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" t="n">
-        <v>31</v>
-      </c>
-      <c r="L10" t="n">
-        <v>32</v>
-      </c>
-      <c r="M10" t="n">
-        <v>37</v>
-      </c>
-      <c r="N10" t="n">
-        <v>44</v>
-      </c>
       <c r="O10" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.14144736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|12|20|31|32|37|44</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
+        <v>46</v>
+      </c>
+      <c r="N11" t="n">
         <v>49</v>
       </c>
-      <c r="N11" t="n">
-        <v>38</v>
-      </c>
       <c r="O11" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.0625</v>
+        <v>35.3667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|18|24|27|40|49|38</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.99107142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|5|22|34|37|40|11</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.7333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -690,25 +690,25 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.3667</v>
+        <v>36.2333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|18|24|34|39|49|47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -788,10 +788,10 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
         <v>34</v>
@@ -800,10 +800,10 @@
         <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O4" t="n">
         <v>151</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.17439230769231</v>
+        <v>36.04099230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>3|11|20|34|38|45|33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="O5" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.00955714285714</v>
+        <v>35.87615714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>5|10|20|31|44|45|40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
         <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.8667</v>
+        <v>35.7333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>3|6|18|32|33|37|39</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.7417</v>
+        <v>35.6083</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|8|12|29|34|45|23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
         <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.63140588235294</v>
+        <v>35.49800588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|12|17|38|44|45|30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
         <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="O9" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.53336666666667</v>
+        <v>35.39996666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>14|19|21|25|38|44|33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
+        <v>31</v>
+      </c>
+      <c r="L10" t="n">
         <v>32</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>38</v>
       </c>
-      <c r="M10" t="n">
-        <v>49</v>
-      </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.44564736842106</v>
+        <v>35.31224736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|12|15|31|32|38|28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1474,22 +1474,22 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="O11" t="n">
         <v>165</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.3667</v>
+        <v>35.2333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|9|20|38|46|49|41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
+        <v>32</v>
+      </c>
+      <c r="L12" t="n">
+        <v>37</v>
+      </c>
+      <c r="M12" t="n">
         <v>38</v>
       </c>
-      <c r="L12" t="n">
-        <v>44</v>
-      </c>
-      <c r="M12" t="n">
-        <v>49</v>
-      </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O12" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.29527142857143</v>
+        <v>35.16187142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>5|6|21|32|37|38|17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.7333</v>
+        <v>74.5333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|25</t>
+          <t>1|3|5|44|46|49|29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
         <v>34</v>
       </c>
       <c r="L3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
         <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.2333</v>
+        <v>36.0333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|18|24|34|39|49|47</t>
+          <t>6|11|20|34|41|45|47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
         <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.04099230769231</v>
+        <v>35.8409923076923</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|11|20|34|38|45|33</t>
+          <t>3|12|18|25|38|41|9</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -883,10 +883,10 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>20</v>
@@ -895,16 +895,16 @@
         <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N5" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.87615714285714</v>
+        <v>35.67615714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5|10|20|31|44|45|40</t>
+          <t>9|19|20|31|40|42|49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.7333</v>
+        <v>35.5333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|6|18|32|33|37|39</t>
+          <t>3|13|24|36|40|49|5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="O7" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.6083</v>
+        <v>35.4083</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|8|12|29|34|45|23</t>
+          <t>3|5|22|32|37|40|38</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
+        <v>37</v>
+      </c>
+      <c r="M8" t="n">
+        <v>40</v>
+      </c>
+      <c r="N8" t="n">
         <v>44</v>
       </c>
-      <c r="M8" t="n">
-        <v>45</v>
-      </c>
-      <c r="N8" t="n">
-        <v>30</v>
-      </c>
       <c r="O8" t="n">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.49800588235294</v>
+        <v>35.29800588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|12|17|38|44|45|30</t>
+          <t>1|3|18|32|37|40|44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O9" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.39996666666666</v>
+        <v>35.19996666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>14|19|21|25|38|44|33</t>
+          <t>3|6|24|25|42|49|37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
         <v>31</v>
@@ -1388,13 +1388,13 @@
         <v>32</v>
       </c>
       <c r="M10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.31224736842105</v>
+        <v>35.11224736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|12|15|31|32|38|28</t>
+          <t>3|12|20|31|32|37|44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="O11" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.2333</v>
+        <v>35.0333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|9|20|38|46|49|41</t>
+          <t>5|6|24|32|33|49|13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.16187142857143</v>
+        <v>34.96187142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|6|21|32|37|38|17</t>
+          <t>3|12|17|38|44|45|30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5333</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|29</t>
+          <t>1|3|42|44|46|49|45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="I3" t="n">
-        <v>11</v>
-      </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
         <v>34</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.0333</v>
+        <v>36.1667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6|11|20|34|41|45|47</t>
+          <t>3|6|24|34|37|49|4</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="O4" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.8409923076923</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|12|18|25|38|41|9</t>
+          <t>3|6|8|29|38|49|35</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N5" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.67615714285714</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|19|20|31|40|42|49</t>
+          <t>3|20|21|25|36|44|4</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
         <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.5333</v>
+        <v>35.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|13|24|36|40|49|5</t>
+          <t>6|15|24|31|44|49|16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
         <v>32</v>
       </c>
       <c r="L7" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.4083</v>
+        <v>35.5417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|5|22|32|37|40|38</t>
+          <t>3|12|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
+        <v>25</v>
+      </c>
+      <c r="L8" t="n">
         <v>32</v>
       </c>
-      <c r="L8" t="n">
-        <v>37</v>
-      </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N8" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.29800588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|3|18|32|37|40|44</t>
+          <t>3|12|20|25|32|33|7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1281,22 +1281,22 @@
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="O9" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.19996666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|37</t>
+          <t>3|6|18|37|44|49|33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="M10" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="O10" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.11224736842105</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|12|20|31|32|37|44</t>
+          <t>3|6|20|29|46|49|15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.0333</v>
+        <v>35.1667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5|6|24|32|33|49|13</t>
+          <t>3|12|17|38|44|45|30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L12" t="n">
         <v>38</v>
-      </c>
-      <c r="L12" t="n">
-        <v>44</v>
       </c>
       <c r="M12" t="n">
         <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="O12" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.96187142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|12|17|38|44|45|30</t>
+          <t>3|14|15|36|38|45|49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|45</t>
+          <t>1|3|42|44|46|49|16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -696,16 +696,16 @@
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
         <v>153</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1667</v>
+        <v>35.9667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|6|24|34|37|49|4</t>
+          <t>3|6|24|29|42|49|28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>42</v>
+      </c>
+      <c r="N4" t="n">
         <v>38</v>
       </c>
-      <c r="M4" t="n">
-        <v>49</v>
-      </c>
-      <c r="N4" t="n">
-        <v>35</v>
-      </c>
       <c r="O4" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.97439230769231</v>
+        <v>35.77439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|6|8|29|38|49|35</t>
+          <t>10|19|20|31|35|42|38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
         <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.80955714285714</v>
+        <v>35.60955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|20|21|25|36|44|4</t>
+          <t>2|3|24|29|36|49|16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
         <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="O6" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6667</v>
+        <v>35.4667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6|15|24|31|44|49|16</t>
+          <t>3|12|20|25|38|49|34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1082,22 +1082,22 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
         <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>161</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5417</v>
+        <v>35.3417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|12|20|32|45|49|42</t>
+          <t>3|9|20|38|42|49|5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="n">
+        <v>29</v>
+      </c>
+      <c r="L8" t="n">
+        <v>34</v>
+      </c>
+      <c r="M8" t="n">
+        <v>37</v>
+      </c>
+      <c r="N8" t="n">
         <v>20</v>
       </c>
-      <c r="K8" t="n">
-        <v>25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32</v>
-      </c>
-      <c r="M8" t="n">
-        <v>33</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7</v>
-      </c>
       <c r="O8" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.43140588235294</v>
+        <v>35.23140588235295</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|12|20|25|32|33|7</t>
+          <t>3|6|24|29|34|37|20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O9" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.33336666666666</v>
+        <v>35.13336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|18|37|44|49|33</t>
+          <t>3|18|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.24564736842105</v>
+        <v>35.04564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|6|20|29|46|49|15</t>
+          <t>3|14|24|25|42|49|8</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1471,16 +1471,16 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
         <v>44</v>
@@ -1489,10 +1489,10 @@
         <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1667</v>
+        <v>34.9667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|12|17|38|44|45|30</t>
+          <t>6|17|20|31|44|45|18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.09527142857143</v>
+        <v>34.89527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|14|15|36|38|45|49</t>
+          <t>3|18|21|37|40|44|13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4667</v>
+        <v>74.5333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|16</t>
+          <t>1|3|42|44|46|49|8</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -690,25 +690,25 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.9667</v>
+        <v>36.0333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|6|24|29|42|49|28</t>
+          <t>3|18|24|25|38|49|8</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -785,37 +785,37 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" t="n">
+        <v>38</v>
+      </c>
+      <c r="N4" t="n">
+        <v>42</v>
+      </c>
+      <c r="O4" t="n">
+        <v>143</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>35</v>
-      </c>
-      <c r="M4" t="n">
-        <v>42</v>
-      </c>
-      <c r="N4" t="n">
-        <v>38</v>
-      </c>
-      <c r="O4" t="n">
-        <v>157</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>32</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.77439230769231</v>
+        <v>35.8409923076923</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>10|19|20|31|35|42|38</t>
+          <t>3|21|24|25|32|38|42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M5" t="n">
         <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="O5" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.60955714285714</v>
+        <v>35.67615714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|3|24|29|36|49|16</t>
+          <t>3|6|24|25|42|49|36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
         <v>20</v>
@@ -993,16 +993,16 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O6" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.4667</v>
+        <v>35.5333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|20|25|38|49|34</t>
+          <t>3|18|20|25|44|45|24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
+        <v>37</v>
+      </c>
+      <c r="L7" t="n">
         <v>38</v>
       </c>
-      <c r="L7" t="n">
-        <v>42</v>
-      </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.3417</v>
+        <v>35.4083</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|9|20|38|42|49|5</t>
+          <t>3|12|23|37|38|46|48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
+        <v>38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" t="n">
         <v>34</v>
       </c>
-      <c r="M8" t="n">
-        <v>37</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20</v>
-      </c>
       <c r="O8" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.23140588235295</v>
+        <v>35.29800588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|24|29|34|37|20</t>
+          <t>3|11|18|32|38|45|34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.13336666666666</v>
+        <v>35.19996666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|18|20|32|45|49|42</t>
+          <t>3|20|21|25|36|42|4</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="O10" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.04564736842106</v>
+        <v>35.11224736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|14|24|25|42|49|8</t>
+          <t>3|12|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>34.9667</v>
+        <v>35.0333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="O12" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.89527142857143</v>
+        <v>34.96187142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|18|21|37|40|44|13</t>
+          <t>11|19|20|26|38|45|34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -647,12 +647,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|8</t>
+          <t>1|3|42|44|46|49|17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -699,16 +699,16 @@
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|18|24|25|38|49|8</t>
+          <t>3|6|24|25|42|49|36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -843,12 +843,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|21|24|25|32|38|42</t>
+          <t>3|12|23|37|38|46|48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
+        <v>36</v>
+      </c>
+      <c r="M5" t="n">
         <v>42</v>
       </c>
-      <c r="M5" t="n">
-        <v>49</v>
-      </c>
       <c r="N5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O5" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|36</t>
+          <t>9|11|20|27|36|42|44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1082,34 +1082,34 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
+        <v>49</v>
+      </c>
+      <c r="N7" t="n">
+        <v>42</v>
+      </c>
+      <c r="O7" t="n">
+        <v>167</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>46</v>
-      </c>
-      <c r="N7" t="n">
-        <v>48</v>
-      </c>
-      <c r="O7" t="n">
-        <v>159</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|12|23|37|38|46|48</t>
+          <t>3|18|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1180,16 +1180,16 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
+        <v>25</v>
+      </c>
+      <c r="L8" t="n">
         <v>32</v>
-      </c>
-      <c r="L8" t="n">
-        <v>38</v>
       </c>
       <c r="M8" t="n">
         <v>45</v>
@@ -1198,7 +1198,7 @@
         <v>34</v>
       </c>
       <c r="O8" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|11|18|32|38|45|34</t>
+          <t>3|12|20|25|32|45|34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="n">
         <v>20</v>
       </c>
-      <c r="J9" t="n">
-        <v>21</v>
-      </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
         <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|20|21|25|36|42|4</t>
+          <t>3|11|20|29|40|42|44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N10" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|12|20|32|45|49|42</t>
+          <t>3|19|20|36|37|42|10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
         <v>31</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|17|20|31|44|45|18</t>
+          <t>6|20|24|31|37|49|4</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M12" t="n">
+        <v>44</v>
+      </c>
+      <c r="N12" t="n">
         <v>45</v>
       </c>
-      <c r="N12" t="n">
-        <v>34</v>
-      </c>
       <c r="O12" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>11|19|20|26|38|45|34</t>
+          <t>3|18|24|27|35|44|45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5333</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|17</t>
+          <t>1|3|42|44|46|49|29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
         <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.0333</v>
+        <v>36.1667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|36</t>
+          <t>4|11|20|31|42|45|3</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -791,22 +791,22 @@
         <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
+        <v>36</v>
+      </c>
+      <c r="M4" t="n">
         <v>38</v>
       </c>
-      <c r="M4" t="n">
-        <v>46</v>
-      </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.8409923076923</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|12|23|37|38|46|48</t>
+          <t>3|12|15|25|36|38|10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N5" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.67615714285714</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|11|20|27|36|42|44</t>
+          <t>11|19|20|31|38|44|8</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.5333</v>
+        <v>35.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|18|20|25|44|45|24</t>
+          <t>3|6|24|25|42|49|36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1079,25 +1079,25 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
+        <v>42</v>
+      </c>
+      <c r="M7" t="n">
         <v>45</v>
       </c>
-      <c r="M7" t="n">
-        <v>49</v>
-      </c>
       <c r="N7" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O7" t="n">
         <v>167</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.4083</v>
+        <v>35.5417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|18|20|32|45|49|42</t>
+          <t>6|19|24|31|42|45|33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M8" t="n">
         <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="O8" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.29800588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|12|20|25|32|45|34</t>
+          <t>3|18|24|25|34|45|20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="O9" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.19996666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|11|20|29|40|42|44</t>
+          <t>3|12|20|25|38|49|34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="O10" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.11224736842105</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|19|20|36|37|42|10</t>
+          <t>3|8|15|38|42|49|40</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1471,25 +1471,25 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" t="n">
         <v>20</v>
       </c>
-      <c r="J11" t="n">
-        <v>24</v>
-      </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="O11" t="n">
         <v>167</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.0333</v>
+        <v>35.1667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|20|24|31|37|49|4</t>
+          <t>3|18|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.96187142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|18|24|27|35|44|45</t>
+          <t>3|12|20|25|32|45|34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -647,12 +647,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|29</t>
+          <t>1|3|42|44|46|49|8</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="O3" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4|11|20|31|42|45|3</t>
+          <t>3|6|24|36|37|49|33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
         <v>25</v>
       </c>
       <c r="L4" t="n">
+        <v>42</v>
+      </c>
+      <c r="M4" t="n">
+        <v>49</v>
+      </c>
+      <c r="N4" t="n">
         <v>36</v>
       </c>
-      <c r="M4" t="n">
-        <v>38</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10</v>
-      </c>
       <c r="O4" t="n">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -843,12 +843,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|12|15|25|36|38|10</t>
+          <t>3|6|24|25|42|49|36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" t="n">
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>11|19|20|31|38|44|8</t>
+          <t>3|18|20|25|44|45|24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M6" t="n">
         <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|36</t>
+          <t>2|3|24|40|47|49|9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1079,25 +1079,25 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O7" t="n">
         <v>167</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|19|24|31|42|45|33</t>
+          <t>2|13|24|39|40|49|36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1180,13 +1180,13 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
         <v>34</v>
@@ -1195,10 +1195,10 @@
         <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="O8" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|18|24|25|34|45|20</t>
+          <t>3|15|24|32|34|45|41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|12|20|25|38|49|34</t>
+          <t>3|10|14|38|45|49|8</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
         <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|40</t>
+          <t>3|11|20|31|42|46|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
         <v>18</v>
       </c>
-      <c r="J11" t="n">
-        <v>20</v>
-      </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O11" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|18|20|32|45|49|42</t>
+          <t>3|9|18|38|42|49|33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
         <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N12" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|12|20|25|32|45|34</t>
+          <t>3|19|20|36|37|42|10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|8</t>
+          <t>1|3|42|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -690,22 +690,22 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" t="n">
         <v>155</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1667</v>
+        <v>35.9667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|6|24|36|37|49|33</t>
+          <t>3|14|18|37|38|45|34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.97439230769231</v>
+        <v>35.77439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|36</t>
+          <t>11|20|22|29|32|49|47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
         <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="O5" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.80955714285714</v>
+        <v>35.60955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|18|20|25|44|45|24</t>
+          <t>3|6|24|25|42|49|37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6667</v>
+        <v>35.4667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|3|24|40|47|49|9</t>
+          <t>3|12|20|31|32|45|34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N7" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5417</v>
+        <v>35.3417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2|13|24|39|40|49|36</t>
+          <t>1|20|21|29|42|44|6</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K8" t="n">
+        <v>29</v>
+      </c>
+      <c r="L8" t="n">
+        <v>46</v>
+      </c>
+      <c r="M8" t="n">
+        <v>49</v>
+      </c>
+      <c r="N8" t="n">
         <v>15</v>
-      </c>
-      <c r="J8" t="n">
-        <v>24</v>
-      </c>
-      <c r="K8" t="n">
-        <v>32</v>
-      </c>
-      <c r="L8" t="n">
-        <v>34</v>
-      </c>
-      <c r="M8" t="n">
-        <v>45</v>
-      </c>
-      <c r="N8" t="n">
-        <v>41</v>
       </c>
       <c r="O8" t="n">
         <v>153</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.43140588235294</v>
+        <v>35.23140588235295</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|15|24|32|34|45|41</t>
+          <t>3|6|20|29|46|49|15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
+        <v>42</v>
+      </c>
+      <c r="M9" t="n">
         <v>45</v>
       </c>
-      <c r="M9" t="n">
-        <v>49</v>
-      </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="O9" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.33336666666666</v>
+        <v>35.13336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|10|14|38|45|49|8</t>
+          <t>1|4|20|33|42|45|29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
+        <v>40</v>
+      </c>
+      <c r="M10" t="n">
         <v>42</v>
       </c>
-      <c r="M10" t="n">
-        <v>46</v>
-      </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.24564736842105</v>
+        <v>35.04564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|11|20|31|42|46|4</t>
+          <t>3|20|21|29|40|42|30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
+        <v>37</v>
+      </c>
+      <c r="M11" t="n">
         <v>42</v>
       </c>
-      <c r="M11" t="n">
-        <v>49</v>
-      </c>
       <c r="N11" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1667</v>
+        <v>34.9667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|9|18|38|42|49|33</t>
+          <t>3|19|20|36|37|42|10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1572,34 +1572,34 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N12" t="n">
+        <v>22</v>
+      </c>
+      <c r="O12" t="n">
+        <v>151</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>42</v>
-      </c>
-      <c r="N12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O12" t="n">
-        <v>157</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>39</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.09527142857143</v>
+        <v>34.89527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|19|20|36|37|42|10</t>
+          <t>3|14|18|29|42|45|22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -610,13 +610,13 @@
         <v>32</v>
       </c>
       <c r="O2" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4667</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|32</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -690,25 +690,25 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.9667</v>
+        <v>36.3667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|14|18|37|38|45|34</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.77439230769231</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>11|20|22|29|32|49|47</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.60955714285714</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|37</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
         <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.4667</v>
+        <v>35.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|20|31|32|45|34</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1079,37 +1079,37 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
         <v>20</v>
       </c>
-      <c r="J7" t="n">
-        <v>21</v>
-      </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>149</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>42</v>
-      </c>
-      <c r="M7" t="n">
-        <v>44</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>157</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.3417</v>
+        <v>35.7417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1|20|21|29|42|44|6</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1183,22 +1183,22 @@
         <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.23140588235295</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|20|29|46|49|15</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.13336666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|4|20|33|42|45|29</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.04564736842106</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|21|29|40|42|30</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1474,25 +1474,25 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="O11" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>34.9667</v>
+        <v>35.3667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|19|20|36|37|42|10</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34.89527142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|14|18|29|42|45|22</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -647,12 +647,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|42|44|46|49|14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -690,25 +690,25 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|12|24|29|34|45|13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>42</v>
+      </c>
+      <c r="N4" t="n">
         <v>38</v>
       </c>
-      <c r="M4" t="n">
-        <v>49</v>
-      </c>
-      <c r="N4" t="n">
-        <v>17</v>
-      </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -843,12 +843,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>10|19|20|31|35|42|38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>3|20|24|29|38|45|15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
         <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>2|11|20|37|44|49|32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|18|21|38|40|49|15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
         <v>38</v>
       </c>
-      <c r="L8" t="n">
-        <v>40</v>
-      </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|21|24|34|38|45|29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
         <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|21|24|25|38|46|1</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|9|24|37|38|44|6</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O11" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>14|15|20|31|34|45|33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1572,22 +1572,22 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
+        <v>37</v>
+      </c>
+      <c r="L12" t="n">
         <v>38</v>
       </c>
-      <c r="L12" t="n">
-        <v>44</v>
-      </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O12" t="n">
         <v>149</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|5|20|37|38|46|30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|14</t>
+          <t>1|3|42|44|46|49|19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.3667</v>
+        <v>36.1667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|12|24|29|34|45|13</t>
+          <t>6|11|20|32|37|49|4</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
         <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M4" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O4" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.17439230769231</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>10|19|20|31|35|42|38</t>
+          <t>5|6|24|31|32|49|45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.00955714285714</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|20|24|29|38|45|15</t>
+          <t>3|17|24|34|39|40|33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
         <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O6" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.8667</v>
+        <v>35.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|11|20|37|44|49|32</t>
+          <t>3|20|23|32|38|49|14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
         <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.7417</v>
+        <v>35.5417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|18|21|38|40|49|15</t>
+          <t>3|6|24|25|42|49|37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="O8" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.63140588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|21|24|34|38|45|29</t>
+          <t>6|11|20|40|41|49|23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.53336666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|21|24|25|38|46|1</t>
+          <t>5|6|19|31|32|34|17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
+        <v>36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N10" t="n">
         <v>38</v>
       </c>
-      <c r="M10" t="n">
-        <v>44</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6</v>
-      </c>
       <c r="O10" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.44564736842106</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|9|24|37|38|44|6</t>
+          <t>3|6|24|25|36|41|38</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L11" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.3667</v>
+        <v>35.1667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>14|15|20|31|34|45|33</t>
+          <t>4|11|20|35|45|46|41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1572,34 +1572,34 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
         <v>38</v>
       </c>
       <c r="M12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N12" t="n">
+        <v>41</v>
+      </c>
+      <c r="O12" t="n">
+        <v>159</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>46</v>
-      </c>
-      <c r="N12" t="n">
-        <v>30</v>
-      </c>
-      <c r="O12" t="n">
-        <v>149</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.29527142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|5|20|37|38|46|30</t>
+          <t>3|14|24|31|38|49|41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_teatime_ensemble_predictions.xlsx
@@ -643,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
@@ -696,19 +696,19 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.1667</v>
+        <v>35.9667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6|11|20|32|37|49|4</t>
+          <t>10|11|20|35|44|45|7</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="O4" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.97439230769231</v>
+        <v>35.77439230769231</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5|6|24|31|32|49|45</t>
+          <t>1|15|20|34|42|45|41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M5" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.80955714285714</v>
+        <v>35.60955714285714</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|17|24|34|39|40|33</t>
+          <t>3|6|24|25|42|49|37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.6667</v>
+        <v>35.4667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
+        <v>35</v>
+      </c>
+      <c r="M7" t="n">
         <v>42</v>
       </c>
-      <c r="M7" t="n">
-        <v>49</v>
-      </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.5417</v>
+        <v>35.3417</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|37</t>
+          <t>10|19|20|31|35|42|39</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="O8" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.43140588235294</v>
+        <v>35.23140588235295</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|11|20|40|41|49|23</t>
+          <t>3|12|20|25|38|49|35</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1281,22 +1281,22 @@
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M9" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.33336666666666</v>
+        <v>35.13336666666666</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|6|19|31|32|34|17</t>
+          <t>5|6|24|32|33|49|14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O10" t="n">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>35.24564736842105</v>
+        <v>35.04564736842106</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|6|24|25|36|41|38</t>
+          <t>3|16|24|36|41|49|20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1471,37 +1471,37 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>11</v>
-      </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
+        <v>49</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>143</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>46</v>
-      </c>
-      <c r="N11" t="n">
-        <v>41</v>
-      </c>
-      <c r="O11" t="n">
-        <v>161</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>42</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.1667</v>
+        <v>34.9667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4|11|20|35|45|46|41</t>
+          <t>3|4|5|38|44|49|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
@@ -1581,16 +1581,16 @@
         <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.09527142857143</v>
+        <v>34.89527142857143</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|14|24|31|38|49|41</t>
+          <t>3|6|24|31|40|45|10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
